--- a/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260923.xlsx
+++ b/Project_ETF/ETF_Investment_Portfolio/009819/ETF_Investment_Portfolio_20260923.xlsx
@@ -616,51 +616,51 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>26.75%</t>
+          <t>26.44%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
-          <t>ORCL US</t>
+          <t>GEV US</t>
         </is>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>甲骨文公司</t>
+          <t>奇異維諾瓦公司</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>100,190</t>
+          <t>15,685</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>7.93%</t>
+          <t>8.05%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
         <is>
-          <t>GEV US</t>
+          <t>ORCL US</t>
         </is>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>奇異維諾瓦公司</t>
+          <t>甲骨文公司</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>15,685</t>
+          <t>100,190</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>7.91%</t>
+          <t>7.81%</t>
         </is>
       </c>
     </row>
@@ -682,7 +682,7 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>7.09%</t>
+          <t>7.16%</t>
         </is>
       </c>
     </row>
@@ -704,7 +704,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>5.11%</t>
+          <t>5.04%</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>4.36%</t>
+          <t>4.55%</t>
         </is>
       </c>
     </row>
@@ -748,7 +748,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>3.44%</t>
+          <t>3.49%</t>
         </is>
       </c>
     </row>
@@ -770,7 +770,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>3.22%</t>
+          <t>3.21%</t>
         </is>
       </c>
     </row>
@@ -792,51 +792,51 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>2.96%</t>
+          <t>2.94%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="inlineStr">
         <is>
-          <t>DUK US</t>
+          <t>CEG US</t>
         </is>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>杜克能源公司</t>
+          <t>星座能源公司</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>45,245</t>
+          <t>19,825</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.82%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="inlineStr">
         <is>
-          <t>CEG US</t>
+          <t>DUK US</t>
         </is>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>星座能源公司</t>
+          <t>杜克能源公司</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>19,825</t>
+          <t>45,245</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>2.77%</t>
+          <t>2.78%</t>
         </is>
       </c>
     </row>
@@ -858,7 +858,7 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>2.50%</t>
+          <t>2.59%</t>
         </is>
       </c>
     </row>
@@ -902,7 +902,7 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>2.00%</t>
+          <t>1.99%</t>
         </is>
       </c>
     </row>
@@ -924,7 +924,7 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>1.69%</t>
+          <t>1.68%</t>
         </is>
       </c>
     </row>
@@ -946,51 +946,51 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>1.54%</t>
+          <t>1.55%</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>NBIS US</t>
+          <t>VST US</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>尼比厄斯集團公眾有限公司</t>
+          <t>維斯達能源公司</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>11,681</t>
+          <t>19,490</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>1.46%</t>
+          <t>1.45%</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>VST US</t>
+          <t>NBIS US</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>維斯達能源公司</t>
+          <t>尼比厄斯集團公眾有限公司</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>19,490</t>
+          <t>11,681</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.43%</t>
         </is>
       </c>
     </row>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.42%</t>
         </is>
       </c>
     </row>
@@ -1034,7 +1034,7 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>1.38%</t>
+          <t>1.37%</t>
         </is>
       </c>
     </row>
@@ -1056,7 +1056,7 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>1.32%</t>
+          <t>1.30%</t>
         </is>
       </c>
     </row>
@@ -1122,7 +1122,7 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>0.97%</t>
+          <t>1.00%</t>
         </is>
       </c>
     </row>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>0.90%</t>
+          <t>0.92%</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.85%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>0.86%</t>
+          <t>0.84%</t>
         </is>
       </c>
     </row>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>0.81%</t>
+          <t>0.82%</t>
         </is>
       </c>
     </row>
